--- a/templates/CAPITANIA C051 - template.xlsx
+++ b/templates/CAPITANIA C051 - template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$43</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -823,15 +823,15 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1250,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="54" min="1" max="1"/>
@@ -1258,8 +1258,8 @@
     <col width="5.42578125" customWidth="1" style="54" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="54" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="54" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="54" min="10" max="15"/>
-    <col width="9.140625" customWidth="1" style="54" min="16" max="16384"/>
+    <col width="9.140625" customWidth="1" style="54" min="10" max="16"/>
+    <col width="9.140625" customWidth="1" style="54" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1403,20 +1403,20 @@
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>0.7628338</v>
+        <v>0.7542513</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>-0.001670962292631417</v>
+        <v>-0.001020500335222163</v>
       </c>
       <c r="E17" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>-3.079193281550162</v>
+        <v>-1.880543797961639</v>
       </c>
       <c r="G17" s="4" t="n"/>
     </row>
@@ -1424,20 +1424,20 @@
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>0.7641106</v>
+        <v>0.7550218</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>-0.001219799441548375</v>
+        <v>-0.001287706418280687</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>-2.247805508129978</v>
+        <v>-2.372942207771017</v>
       </c>
       <c r="G18" s="4" t="n"/>
     </row>
@@ -1445,20 +1445,20 @@
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>0.7650438000000001</v>
+        <v>0.7559953</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>-0.001594486298223452</v>
+        <v>-0.001272592715110155</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>-2.938265883475826</v>
+        <v>-2.345091182366512</v>
       </c>
       <c r="G19" s="4" t="n"/>
     </row>
@@ -1466,20 +1466,20 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>0.7662656</v>
+        <v>0.7569586</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>-0.001619005503784798</v>
+        <v>-0.001506528090529313</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>-2.983449053297419</v>
+        <v>-2.77617944778345</v>
       </c>
       <c r="G20" s="4" t="n"/>
     </row>
@@ -1487,20 +1487,20 @@
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>0.7675082</v>
+        <v>0.7581007</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>-0.002529843208463944</v>
+        <v>-0.001913228277808932</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>-4.661910232941315</v>
+        <v>-3.525632915284784</v>
       </c>
       <c r="G21" s="4" t="n"/>
     </row>
@@ -1541,18 +1541,18 @@
     <row r="24" ht="15.95" customHeight="1">
       <c r="B24" s="41" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="41" t="inlineStr"/>
       <c r="D24" s="39" t="n">
-        <v>-0.03862046384885376</v>
+        <v>-0.009378870787109417</v>
       </c>
       <c r="E24" s="39" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>-3.683975018069324</v>
+        <v>-2.464993190165003</v>
       </c>
       <c r="G24" s="17" t="n"/>
     </row>
@@ -1565,13 +1565,13 @@
       </c>
       <c r="C25" s="42" t="inlineStr"/>
       <c r="D25" s="12" t="n">
-        <v>-0.04375815975475761</v>
+        <v>-0.03236358178165388</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>-3.772952801914197</v>
+        <v>-2.811676674591521</v>
       </c>
       <c r="G25" s="19" t="n"/>
     </row>
@@ -1584,13 +1584,13 @@
       </c>
       <c r="C26" s="42" t="inlineStr"/>
       <c r="D26" s="12" t="n">
-        <v>-0.2694232808241016</v>
+        <v>-0.1061157576024768</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>-7.634953213627734</v>
+        <v>-3.014767318679133</v>
       </c>
       <c r="G26" s="19" t="n"/>
     </row>
@@ -1603,13 +1603,13 @@
       </c>
       <c r="C27" s="42" t="inlineStr"/>
       <c r="D27" s="12" t="n">
-        <v>-0.4591748258312408</v>
+        <v>-0.4670808814739051</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>-6.389154815174743</v>
+        <v>-6.507551813481392</v>
       </c>
       <c r="G27" s="19" t="n"/>
     </row>
@@ -1622,13 +1622,13 @@
       </c>
       <c r="C28" s="42" t="inlineStr"/>
       <c r="D28" s="20" t="n">
-        <v>-0.415896274267887</v>
+        <v>-0.4259592172601151</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>-2.8135899922376</v>
+        <v>-2.877791001672949</v>
       </c>
       <c r="G28" s="19" t="n"/>
     </row>
@@ -1636,18 +1636,18 @@
       <c r="A29" s="22" t="n"/>
       <c r="B29" s="42" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C29" s="42" t="inlineStr"/>
       <c r="D29" s="20" t="n">
-        <v>-0.1055479366604037</v>
+        <v>-0.3507155330614133</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>-3.253733334929795</v>
+        <v>-1.261882277060118</v>
       </c>
       <c r="G29" s="19" t="n"/>
     </row>
@@ -1655,18 +1655,18 @@
       <c r="A30" s="22" t="n"/>
       <c r="B30" s="42" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C30" s="42" t="inlineStr"/>
       <c r="D30" s="20" t="n">
-        <v>-0.3261804280729449</v>
+        <v>-0.1156112490537614</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>-2.278866474937467</v>
+        <v>-3.037973502599717</v>
       </c>
       <c r="G30" s="19" t="n"/>
     </row>
@@ -1674,18 +1674,18 @@
       <c r="A31" s="22" t="n"/>
       <c r="B31" s="42" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C31" s="42" t="inlineStr"/>
       <c r="D31" s="20" t="n">
-        <v>0.1348022965101816</v>
+        <v>-0.3261804280729449</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>1.234397576280476</v>
+        <v>-2.278866474937467</v>
       </c>
       <c r="G31" s="19" t="n"/>
     </row>
@@ -1693,161 +1693,180 @@
       <c r="A32" s="22" t="n"/>
       <c r="B32" s="42" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C32" s="42" t="inlineStr"/>
       <c r="D32" s="20" t="n">
-        <v>-0.2371662</v>
+        <v>0.1348022965101816</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>0.4806558014426232</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>-0.4934221105584866</v>
+        <v>1.234397576280476</v>
       </c>
       <c r="G32" s="19" t="n"/>
     </row>
     <row r="33" ht="15.95" customHeight="1">
       <c r="A33" s="22" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="26.1" customHeight="1">
+      <c r="B33" s="42" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C33" s="42" t="inlineStr"/>
+      <c r="D33" s="20" t="n">
+        <v>-0.2457487</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>0.4887104127977628</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>-0.5028513687546398</v>
+      </c>
+      <c r="G33" s="19" t="n"/>
+    </row>
+    <row r="34" ht="15.95" customHeight="1">
       <c r="A34" s="22" t="n"/>
-      <c r="B34" s="55" t="inlineStr">
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="26.1" customHeight="1">
+      <c r="A35" s="22" t="n"/>
+      <c r="B35" s="53" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="A35" s="25" t="n"/>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="n"/>
-      <c r="D35" s="24" t="n"/>
-      <c r="E35" s="43" t="n">
-        <v>301260.559</v>
-      </c>
-      <c r="F35" s="43" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="25" t="n"/>
-      <c r="B36" s="26" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C36" s="24" t="n"/>
       <c r="D36" s="24" t="n"/>
       <c r="E36" s="43" t="n">
-        <v>17857804.36948294</v>
+        <v>297871.1446999999</v>
       </c>
       <c r="F36" s="43" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="25" t="n"/>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="24" t="n"/>
+      <c r="E37" s="43" t="n">
+        <v>16310731.31138095</v>
+      </c>
+      <c r="F37" s="43" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
-      <c r="A38" s="31" t="n"/>
-      <c r="B38" s="28" t="inlineStr">
+      <c r="A38" s="25" t="n"/>
+      <c r="B38" s="27" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="15.95" customHeight="1">
+      <c r="A39" s="31" t="n"/>
+      <c r="B39" s="28" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C38" s="29" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="30" t="n"/>
-      <c r="F38" s="30" t="n"/>
-      <c r="G38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="29" t="inlineStr">
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D39" s="30" t="n"/>
+      <c r="E39" s="30" t="n"/>
+      <c r="F39" s="30" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="B40" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C39" s="29" t="inlineStr">
+      <c r="C40" s="29" t="inlineStr">
         <is>
           <t>2022-12-29</t>
         </is>
       </c>
-      <c r="D39" s="32" t="n"/>
-      <c r="E39" s="32" t="n"/>
-      <c r="F39" s="32" t="n"/>
-      <c r="G39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="15.95" customHeight="1">
-      <c r="B40" s="33" t="n"/>
-      <c r="C40" s="34" t="n"/>
       <c r="D40" s="32" t="n"/>
       <c r="E40" s="32" t="n"/>
       <c r="F40" s="32" t="n"/>
       <c r="G40" s="4" t="n"/>
     </row>
-    <row r="41" ht="54" customHeight="1">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="56" t="inlineStr">
+    <row r="41" ht="15.95" customHeight="1">
+      <c r="B41" s="33" t="n"/>
+      <c r="C41" s="34" t="n"/>
+      <c r="D41" s="32" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="54" customHeight="1">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="55" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="53" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="35" t="n"/>
-      <c r="C43" s="35" t="n"/>
-      <c r="D43" s="35" t="n"/>
-      <c r="E43" s="35" t="n"/>
-      <c r="F43" s="35" t="n"/>
+      <c r="B43" s="56" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="36" t="n"/>
-      <c r="C44" s="37" t="n"/>
-      <c r="D44" s="19" t="n"/>
-      <c r="E44" s="19" t="n"/>
-      <c r="F44" s="19" t="n"/>
+      <c r="B44" s="35" t="n"/>
+      <c r="C44" s="35" t="n"/>
+      <c r="D44" s="35" t="n"/>
+      <c r="E44" s="35" t="n"/>
+      <c r="F44" s="35" t="n"/>
       <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="4" t="n"/>
       <c r="B45" s="36" t="n"/>
       <c r="C45" s="37" t="n"/>
       <c r="D45" s="19" t="n"/>
       <c r="E45" s="19" t="n"/>
       <c r="F45" s="19" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="36" t="n"/>
+      <c r="C46" s="37" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="86" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="83"/>
 </worksheet>
 </file>